--- a/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/2. location_area [21,24-28,6]/27. city_wip.xlsx
+++ b/2. Components/2.1. Cloud Component/2.1.1. Autonomous_Database/3. autonomous_db_owner (wip)/4. dml/2. location_area [21,24-28,6]/27. city_wip.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D8DD183-0BC0-4374-BD65-F5616FC07F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
